--- a/TestCases/Doctor_Work_Schedule_TestCase.xlsx
+++ b/TestCases/Doctor_Work_Schedule_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D58CB8-C51D-44D9-A883-85F0CD74B802}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A81315-E4AF-44E4-9AC8-A57EBE49A67C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="WORKSCHEDULE" sheetId="11" r:id="rId1"/>
+    <sheet name="WORKSCHEDULE" sheetId="12" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -34,19 +34,19 @@
     <t>SpringMediCareWeb</t>
   </si>
   <si>
-    <t>Module Code：</t>
+    <t>Pass</t>
   </si>
   <si>
-    <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Module Code：</t>
+  </si>
+  <si>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -76,10 +76,10 @@
     <t>Note</t>
   </si>
   <si>
-    <t>WORKSCHEDULE400 - Doctor Schedule</t>
+    <t>SCHEDULE - Doctor Work Schedule</t>
   </si>
   <si>
-    <t>WORKSCHEDULE1 - Doctor Work Schedule</t>
+    <t>Doctor Work Schedule</t>
   </si>
   <si>
     <t>1. Kiểm tra lịch làm việc theo tuần của bác sĩ</t>
@@ -94,9 +94,9 @@
     <t>1: Đăng nhập bằng tài khoản Doctor có lịch làm việc.
 2: Mở trang Lịch làm việc của tôi.
 3: Kiểm tra tên Doctor và chuyên khoa hiển thị trên trang.
-4: Kiểm tra khoảng thời gian của tuần đang hiển thị.
-5: Kiểm tra các ngày và ca làm việc trong bảng lịch theo tuần.
-6: Kiểm tra các ô có lịch và các ô không có lịch.</t>
+4: Kiểm tra khoảng thời gian và 7 ngày của tuần đang hiển thị.
+5: Kiểm tra các ca Sáng, Chiều, Tối trong bảng lịch theo tuần.
+6: Kiểm tra các ca có lịch hiển thị đúng Doctor và các ca không có lịch hiển thị “Trống”.</t>
   </si>
   <si>
     <t>Hiển thị đúng tên Doctor đang đăng nhập.
@@ -119,11 +119,11 @@
     <t>Kiểm tra chức năng Tuần trước hiển thị đúng lịch làm việc của Doctor trong tuần liền trước.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng Doctor.
+    <t>1: Đăng nhập bằng tài khoản Doctor.
 2: Mở trang Lịch làm việc của tôi và ghi nhận tuần đang hiển thị.
 3: Nhấn Tuần trước.
-4: Kiểm tra khoảng ngày sau khi chuyển tuần.
-5: Kiểm tra dữ liệu lịch làm việc được hiển thị.</t>
+4: Kiểm tra khoảng thời gian và các ngày sau khi chuyển tuần.
+5: Kiểm tra dữ liệu lịch làm việc thuộc tuần vừa chọn.</t>
   </si>
   <si>
     <t>Khoảng thời gian chuyển đúng về tuần liền trước.
@@ -145,11 +145,11 @@
     <t>Kiểm tra chức năng Tuần sau hiển thị đúng lịch làm việc của Doctor trong tuần kế tiếp.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng Doctor.
+    <t>1: Đăng nhập bằng tài khoản Doctor.
 2: Mở trang Lịch làm việc của tôi và ghi nhận tuần đang hiển thị.
 3: Nhấn Tuần sau.
-4: Kiểm tra khoảng ngày sau khi chuyển tuần.
-5: Kiểm tra dữ liệu lịch làm việc được hiển thị.</t>
+4: Kiểm tra khoảng thời gian và các ngày sau khi chuyển tuần.
+5: Kiểm tra dữ liệu lịch làm việc thuộc tuần vừa chọn.</t>
   </si>
   <si>
     <t>Khoảng thời gian chuyển đúng sang tuần kế tiếp.
@@ -174,12 +174,12 @@
     <t>Kiểm tra thông tin lịch làm việc trong bảng Lịch làm việc theo tuần khớp với dữ liệu trong Danh sách lịch làm việc của Doctor.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng Doctor có lịch làm việc.
+    <t>1: Đăng nhập bằng tài khoản Doctor có lịch làm việc.
 2: Mở trang Lịch làm việc của tôi.
-3: Chọn một ngày có ít nhất một ca làm việc trong bảng Lịch làm việc theo tuần.
-4: Ghi nhận ngày, ca làm việc và thời gian của ca đó.
-5: Kiểm tra Danh sách lịch làm việc phía dưới.
-6: Đối chiếu các bản ghi tương ứng.</t>
+3: Ghi nhận các lịch làm việc đang hiển thị trong bảng Lịch làm việc theo tuần.
+4: Mở khu vực Danh sách lịch làm việc phía dưới.
+5: Ghi nhận các lịch làm việc trong danh sách.
+6: Đối chiếu Doctor, ngày, ca và thời gian giữa hai khu vực.</t>
   </si>
   <si>
     <t>Mỗi ca có lịch trong bảng theo tuần có bản ghi tương ứng trong danh sách lịch làm việc.
@@ -203,11 +203,12 @@
   </si>
   <si>
     <t>1: Đăng nhập bằng Doctor A.
-2: Mở Lịch làm việc của tôi và ghi nhận tên Doctor, chuyên khoa và một số lịch đang hiển thị.
+2: Mở Lịch làm việc của tôi và ghi nhận tên Doctor, chuyên khoa và lịch đang hiển thị.
 3: Đăng xuất Doctor A.
 4: Đăng nhập bằng Doctor B.
-5: Mở Lịch làm việc của tôi.
-6: So sánh thông tin và lịch làm việc của hai Doctor.</t>
+5: Mở Lịch làm việc của tôi và ghi nhận tên Doctor, chuyên khoa và lịch đang hiển thị.
+6: Kiểm tra Doctor B chỉ thấy thông tin và lịch làm việc của mình.
+7: Đối chiếu dữ liệu Doctor A và Doctor B để bảo đảm không bị lẫn lịch.</t>
   </si>
   <si>
     <t>Khi đăng nhập Doctor A, hệ thống hiển thị đúng tên, chuyên khoa và lịch làm việc của Doctor A.
@@ -242,10 +243,6 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +252,10 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -443,10 +444,10 @@
   </cellStyleXfs>
   <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -462,10 +463,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -484,32 +485,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -749,9 +750,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -775,9 +776,9 @@
     </row>
     <row r="2" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -803,11 +804,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -831,13 +832,13 @@
     </row>
     <row r="4" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -861,13 +862,13 @@
     </row>
     <row r="5" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -891,13 +892,13 @@
     </row>
     <row r="6" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -925,7 +926,7 @@
     </row>
     <row r="7" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -984,21 +985,21 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="29" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="27" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="32" t="s">
@@ -1026,16 +1027,16 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1054,14 +1055,14 @@
     <row r="11" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="35"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="22"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1081,15 +1082,15 @@
       <c r="A12" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="22"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1105,7 +1106,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:24" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>20</v>
       </c>
@@ -1118,8 +1119,8 @@
       <c r="D13" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="17" t="s">
         <v>24</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>46247</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>25</v>
@@ -1160,8 +1161,8 @@
       <c r="D14" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
       <c r="G14" s="17" t="s">
         <v>30</v>
       </c>
@@ -1169,7 +1170,7 @@
         <v>46247</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>31</v>
@@ -1202,8 +1203,8 @@
       <c r="D15" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="17" t="s">
         <v>36</v>
       </c>
@@ -1211,7 +1212,7 @@
         <v>46247</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>37</v>
@@ -1235,15 +1236,15 @@
       <c r="A16" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="22"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1272,8 +1273,8 @@
       <c r="D17" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="17" t="s">
         <v>43</v>
       </c>
@@ -1281,7 +1282,7 @@
         <v>46247</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>44</v>
@@ -1314,8 +1315,8 @@
       <c r="D18" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
       <c r="G18" s="17" t="s">
         <v>49</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>46247</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>50</v>
@@ -26373,19 +26374,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="J9:J10"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
@@ -26395,11 +26396,11 @@
     <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
-    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
-    <hyperlink ref="G15" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000002000000}"/>
-    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0A00-000003000000}"/>
-    <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0B00-000001000000}"/>
+    <hyperlink ref="G15" r:id="rId3" xr:uid="{00000000-0004-0000-0B00-000002000000}"/>
+    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
+    <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
